--- a/DOM/AFOLU/_GDP_Ref.xlsx
+++ b/DOM/AFOLU/_GDP_Ref.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="24827"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="6" rupBuild="28526"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\luisf\Dropbox\2_WORK\EperLab\2_Herramientas\_mmf_GUA\OSeMOSYS_GUA_RDM_v20220213\Experiment_1\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="https://clgcr.sharepoint.com/sites/ClimateLeadGroup-Decarb_RD/Documentos compartidos/Decarb_RD/WBG/04_Model/RD_model_int_NZ6/"/>
     </mc:Choice>
   </mc:AlternateContent>
   <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{FAECB850-8779-4D04-BDEB-D9EE599BA306}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-25635" yWindow="2955" windowWidth="21510" windowHeight="10710" activeTab="1" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="28680" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="GDP" sheetId="1" r:id="rId1"/>
@@ -584,16 +584,16 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <dimension ref="A1:E34"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="13.53515625" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="11.53515625" bestFit="1" customWidth="1"/>
-    <col min="4" max="4" width="14.61328125" bestFit="1" customWidth="1"/>
-    <col min="5" max="5" width="11.07421875" bestFit="1" customWidth="1"/>
-    <col min="7" max="7" width="9.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="13.5546875" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="11.5546875" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="14.6640625" bestFit="1" customWidth="1"/>
+    <col min="5" max="5" width="11.109375" bestFit="1" customWidth="1"/>
+    <col min="7" max="7" width="9.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="1" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A1" s="2" t="s">
         <v>0</v>
       </c>
@@ -604,7 +604,7 @@
         <v>2</v>
       </c>
     </row>
-    <row r="2" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A2" s="2">
         <v>2018</v>
       </c>
@@ -614,7 +614,7 @@
       <c r="D2" s="3"/>
       <c r="E2" s="3"/>
     </row>
-    <row r="3" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A3" s="2">
         <v>2019</v>
       </c>
@@ -622,7 +622,7 @@
         <v>70634</v>
       </c>
     </row>
-    <row r="4" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A4" s="1">
         <v>2020</v>
       </c>
@@ -630,7 +630,7 @@
         <v>69561</v>
       </c>
     </row>
-    <row r="5" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A5" s="1">
         <v>2021</v>
       </c>
@@ -642,7 +642,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="6" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A6" s="1">
         <v>2022</v>
       </c>
@@ -654,7 +654,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="7" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A7" s="1">
         <v>2023</v>
       </c>
@@ -666,7 +666,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="8" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A8" s="1">
         <v>2024</v>
       </c>
@@ -678,7 +678,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="9" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A9" s="1">
         <v>2025</v>
       </c>
@@ -690,7 +690,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="10" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A10" s="1">
         <v>2026</v>
       </c>
@@ -702,7 +702,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="11" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A11" s="1">
         <v>2027</v>
       </c>
@@ -714,7 +714,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="12" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A12" s="1">
         <v>2028</v>
       </c>
@@ -726,7 +726,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="13" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A13" s="1">
         <v>2029</v>
       </c>
@@ -738,7 +738,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="14" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A14" s="1">
         <v>2030</v>
       </c>
@@ -750,7 +750,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="15" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A15" s="1">
         <v>2031</v>
       </c>
@@ -762,7 +762,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="16" spans="1:5" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.3">
       <c r="A16" s="1">
         <v>2032</v>
       </c>
@@ -774,7 +774,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="1">
         <v>2033</v>
       </c>
@@ -786,7 +786,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="1">
         <v>2034</v>
       </c>
@@ -798,7 +798,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="1">
         <v>2035</v>
       </c>
@@ -810,7 +810,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="1">
         <v>2036</v>
       </c>
@@ -822,7 +822,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="1">
         <v>2037</v>
       </c>
@@ -834,7 +834,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="1">
         <v>2038</v>
       </c>
@@ -846,7 +846,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="1">
         <v>2039</v>
       </c>
@@ -858,7 +858,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="1">
         <v>2040</v>
       </c>
@@ -870,7 +870,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="1">
         <v>2041</v>
       </c>
@@ -882,7 +882,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="1">
         <v>2042</v>
       </c>
@@ -894,7 +894,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="1">
         <v>2043</v>
       </c>
@@ -906,7 +906,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="1">
         <v>2044</v>
       </c>
@@ -918,7 +918,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="1">
         <v>2045</v>
       </c>
@@ -930,7 +930,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="1">
         <v>2046</v>
       </c>
@@ -942,7 +942,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="1">
         <v>2047</v>
       </c>
@@ -954,7 +954,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="1">
         <v>2048</v>
       </c>
@@ -966,7 +966,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="1">
         <v>2049</v>
       </c>
@@ -978,7 +978,7 @@
         <v>3.5</v>
       </c>
     </row>
-    <row r="34" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="34" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A34" s="1">
         <v>2050</v>
       </c>
@@ -1000,13 +1000,13 @@
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{93394259-0791-4AF3-A5C0-DFDE9EDD707A}">
   <dimension ref="A1:C33"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="2" max="2" width="11.3828125" bestFit="1" customWidth="1"/>
-    <col min="3" max="3" width="8.84375" bestFit="1" customWidth="1"/>
+    <col min="2" max="2" width="11.33203125" bestFit="1" customWidth="1"/>
+    <col min="3" max="3" width="8.88671875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="5" t="s">
         <v>0</v>
       </c>
@@ -1017,7 +1017,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="7">
         <v>2019</v>
       </c>
@@ -1028,7 +1028,7 @@
         <v>1.8</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2020</v>
       </c>
@@ -1039,7 +1039,7 @@
         <v>-3.6</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>2021</v>
       </c>
@@ -1050,7 +1050,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>2022</v>
       </c>
@@ -1061,7 +1061,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>2023</v>
       </c>
@@ -1072,7 +1072,7 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>2024</v>
       </c>
@@ -1083,182 +1083,182 @@
         <v>1.1000000000000001</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2025</v>
       </c>
       <c r="B8" s="1"/>
       <c r="C8" s="1"/>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>2026</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>2027</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>2028</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>2029</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>2030</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>2031</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>2032</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>2033</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>2034</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>2035</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>2036</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>2037</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>2038</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>2039</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>2040</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>2041</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>2042</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>2043</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>2044</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>2045</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>2046</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>2047</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>2048</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>2049</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="33" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A33" s="10">
         <v>2050</v>
       </c>
@@ -1277,14 +1277,14 @@
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{35EF900E-2E45-49F0-9922-4F93E1E42E25}">
   <dimension ref="A1:C34"/>
-  <sheetFormatPr defaultRowHeight="14.6" x14ac:dyDescent="0.4"/>
+  <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
-    <col min="1" max="1" width="7.15234375" customWidth="1"/>
-    <col min="2" max="2" width="11.15234375" customWidth="1"/>
-    <col min="3" max="3" width="11.765625" customWidth="1"/>
+    <col min="1" max="1" width="7.109375" customWidth="1"/>
+    <col min="2" max="2" width="11.109375" customWidth="1"/>
+    <col min="3" max="3" width="11.77734375" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="1" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A1" s="13" t="s">
         <v>0</v>
       </c>
@@ -1295,7 +1295,7 @@
         <v>6</v>
       </c>
     </row>
-    <row r="2" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="2" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A2" s="12">
         <v>2018</v>
       </c>
@@ -1306,7 +1306,7 @@
         <v>617.84772289277112</v>
       </c>
     </row>
-    <row r="3" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="3" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A3" s="9">
         <v>2019</v>
       </c>
@@ -1317,7 +1317,7 @@
         <v>726.66152336268647</v>
       </c>
     </row>
-    <row r="4" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="4" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A4" s="9">
         <v>2020</v>
       </c>
@@ -1328,7 +1328,7 @@
         <v>757.1376149652823</v>
       </c>
     </row>
-    <row r="5" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="5" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A5" s="9">
         <v>2021</v>
       </c>
@@ -1339,7 +1339,7 @@
         <v>749.24155834931821</v>
       </c>
     </row>
-    <row r="6" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="6" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A6" s="9">
         <v>2022</v>
       </c>
@@ -1350,7 +1350,7 @@
         <v>749.24155834931821</v>
       </c>
     </row>
-    <row r="7" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="7" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A7" s="9">
         <v>2023</v>
       </c>
@@ -1361,7 +1361,7 @@
         <v>749.24155834931821</v>
       </c>
     </row>
-    <row r="8" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="8" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A8" s="9">
         <v>2024</v>
       </c>
@@ -1372,182 +1372,182 @@
         <v>749.24155834931821</v>
       </c>
     </row>
-    <row r="9" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="9" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A9" s="9">
         <v>2025</v>
       </c>
       <c r="B9" s="1"/>
       <c r="C9" s="1"/>
     </row>
-    <row r="10" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="10" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A10" s="9">
         <v>2026</v>
       </c>
       <c r="B10" s="1"/>
       <c r="C10" s="1"/>
     </row>
-    <row r="11" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="11" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A11" s="9">
         <v>2027</v>
       </c>
       <c r="B11" s="1"/>
       <c r="C11" s="1"/>
     </row>
-    <row r="12" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="12" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A12" s="9">
         <v>2028</v>
       </c>
       <c r="B12" s="1"/>
       <c r="C12" s="1"/>
     </row>
-    <row r="13" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="13" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A13" s="9">
         <v>2029</v>
       </c>
       <c r="B13" s="1"/>
       <c r="C13" s="1"/>
     </row>
-    <row r="14" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="14" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A14" s="9">
         <v>2030</v>
       </c>
       <c r="B14" s="1"/>
       <c r="C14" s="1"/>
     </row>
-    <row r="15" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="15" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A15" s="9">
         <v>2031</v>
       </c>
       <c r="B15" s="1"/>
       <c r="C15" s="1"/>
     </row>
-    <row r="16" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="16" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A16" s="9">
         <v>2032</v>
       </c>
       <c r="B16" s="1"/>
       <c r="C16" s="1"/>
     </row>
-    <row r="17" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="17" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A17" s="9">
         <v>2033</v>
       </c>
       <c r="B17" s="1"/>
       <c r="C17" s="1"/>
     </row>
-    <row r="18" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="18" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A18" s="9">
         <v>2034</v>
       </c>
       <c r="B18" s="1"/>
       <c r="C18" s="1"/>
     </row>
-    <row r="19" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="19" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A19" s="9">
         <v>2035</v>
       </c>
       <c r="B19" s="1"/>
       <c r="C19" s="1"/>
     </row>
-    <row r="20" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="20" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A20" s="9">
         <v>2036</v>
       </c>
       <c r="B20" s="1"/>
       <c r="C20" s="1"/>
     </row>
-    <row r="21" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="21" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A21" s="9">
         <v>2037</v>
       </c>
       <c r="B21" s="1"/>
       <c r="C21" s="1"/>
     </row>
-    <row r="22" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="22" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A22" s="9">
         <v>2038</v>
       </c>
       <c r="B22" s="1"/>
       <c r="C22" s="1"/>
     </row>
-    <row r="23" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="23" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A23" s="9">
         <v>2039</v>
       </c>
       <c r="B23" s="1"/>
       <c r="C23" s="1"/>
     </row>
-    <row r="24" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="24" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A24" s="9">
         <v>2040</v>
       </c>
       <c r="B24" s="1"/>
       <c r="C24" s="1"/>
     </row>
-    <row r="25" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="25" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A25" s="9">
         <v>2041</v>
       </c>
       <c r="B25" s="1"/>
       <c r="C25" s="1"/>
     </row>
-    <row r="26" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="26" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A26" s="9">
         <v>2042</v>
       </c>
       <c r="B26" s="1"/>
       <c r="C26" s="1"/>
     </row>
-    <row r="27" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="27" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A27" s="9">
         <v>2043</v>
       </c>
       <c r="B27" s="1"/>
       <c r="C27" s="1"/>
     </row>
-    <row r="28" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="28" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A28" s="9">
         <v>2044</v>
       </c>
       <c r="B28" s="1"/>
       <c r="C28" s="1"/>
     </row>
-    <row r="29" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="29" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A29" s="9">
         <v>2045</v>
       </c>
       <c r="B29" s="1"/>
       <c r="C29" s="1"/>
     </row>
-    <row r="30" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="30" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A30" s="9">
         <v>2046</v>
       </c>
       <c r="B30" s="1"/>
       <c r="C30" s="1"/>
     </row>
-    <row r="31" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="31" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A31" s="9">
         <v>2047</v>
       </c>
       <c r="B31" s="1"/>
       <c r="C31" s="1"/>
     </row>
-    <row r="32" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="32" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A32" s="9">
         <v>2048</v>
       </c>
       <c r="B32" s="1"/>
       <c r="C32" s="1"/>
     </row>
-    <row r="33" spans="1:3" x14ac:dyDescent="0.4">
+    <row r="33" spans="1:3" x14ac:dyDescent="0.3">
       <c r="A33" s="9">
         <v>2049</v>
       </c>
       <c r="B33" s="1"/>
       <c r="C33" s="1"/>
     </row>
-    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.45">
+    <row r="34" spans="1:3" ht="15" thickBot="1" x14ac:dyDescent="0.35">
       <c r="A34" s="10">
         <v>2050</v>
       </c>
@@ -1564,10 +1564,28 @@
 </file>
 
 <file path=customXml/item1.xml><?xml version="1.0" encoding="utf-8"?>
-<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Documento" ma:contentTypeID="0x010100CCDA0DC61E44874FB77B81A0A8C300E4" ma:contentTypeVersion="17" ma:contentTypeDescription="Crear nuevo documento." ma:contentTypeScope="" ma:versionID="71904d85c9bd1373b9e56b88e8365113">
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" xmlns:ns3="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="7f50eb003d4f8624802c7eda0096d7ec" ns2:_="" ns3:_="">
-    <xsd:import namespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
-    <xsd:import namespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1"/>
+<p:properties xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls">
+  <documentManagement>
+    <lcf76f155ced4ddcb4097134ff3c332f xmlns="160a8fee-1065-46af-a09f-4bc299cd7729" xsi:nil="true"/>
+    <TaxCatchAll xmlns="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" xsi:nil="true"/>
+  </documentManagement>
+</p:properties>
+</file>
+
+<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
+<?mso-contentType ?>
+<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
+  <Display>DocumentLibraryForm</Display>
+  <Edit>DocumentLibraryForm</Edit>
+  <New>DocumentLibraryForm</New>
+</FormTemplates>
+</file>
+
+<file path=customXml/item3.xml><?xml version="1.0" encoding="utf-8"?>
+<ct:contentTypeSchema xmlns:ct="http://schemas.microsoft.com/office/2006/metadata/contentType" xmlns:ma="http://schemas.microsoft.com/office/2006/metadata/properties/metaAttributes" ct:_="" ma:_="" ma:contentTypeName="Document" ma:contentTypeID="0x0101000D404091916B8749A73FDE0336A1D2B1" ma:contentTypeVersion="20" ma:contentTypeDescription="Create a new document." ma:contentTypeScope="" ma:versionID="97d759966af21adcadc0b99feda85e1a">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:p="http://schemas.microsoft.com/office/2006/metadata/properties" xmlns:ns2="160a8fee-1065-46af-a09f-4bc299cd7729" xmlns:ns3="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" targetNamespace="http://schemas.microsoft.com/office/2006/metadata/properties" ma:root="true" ma:fieldsID="c4a9b885529ac7a0313cb8fba8dc54f0" ns2:_="" ns3:_="">
+    <xsd:import namespace="160a8fee-1065-46af-a09f-4bc299cd7729"/>
+    <xsd:import namespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99"/>
     <xsd:element name="properties">
       <xsd:complexType>
         <xsd:sequence>
@@ -1576,18 +1594,13 @@
               <xsd:all>
                 <xsd:element ref="ns2:MediaServiceMetadata" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceFastMetadata" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceAutoKeyPoints" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceKeyPoints" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceDateTaken" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaLengthInSeconds" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithUsers" minOccurs="0"/>
-                <xsd:element ref="ns3:SharedWithDetails" minOccurs="0"/>
+                <xsd:element ref="ns3:TaxCatchAll" minOccurs="0"/>
+                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
+                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceGenerationTime" minOccurs="0"/>
                 <xsd:element ref="ns2:MediaServiceEventHashCode" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceOCR" minOccurs="0"/>
-                <xsd:element ref="ns2:lcf76f155ced4ddcb4097134ff3c332f" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceObjectDetectorVersions" minOccurs="0"/>
-                <xsd:element ref="ns2:MediaServiceSearchProperties" minOccurs="0"/>
               </xsd:all>
             </xsd:complexType>
           </xsd:element>
@@ -1595,7 +1608,7 @@
       </xsd:complexType>
     </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="9c2c21c4-f980-47d5-be5b-1bb924ee96a2" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="160a8fee-1065-46af-a09f-4bc299cd7729" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
     <xsd:element name="MediaServiceMetadata" ma:index="8" nillable="true" ma:displayName="MediaServiceMetadata" ma:hidden="true" ma:internalName="MediaServiceMetadata" ma:readOnly="true">
@@ -1608,91 +1621,52 @@
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceAutoKeyPoints" ma:index="10" nillable="true" ma:displayName="MediaServiceAutoKeyPoints" ma:hidden="true" ma:internalName="MediaServiceAutoKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceSearchProperties" ma:index="10" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceKeyPoints" ma:index="11" nillable="true" ma:displayName="KeyPoints" ma:internalName="MediaServiceKeyPoints" ma:readOnly="true">
+    <xsd:element name="MediaServiceDateTaken" ma:index="11" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Text"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="13" nillable="true" ma:displayName="Etiquetas de imagen_0" ma:hidden="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f">
+      <xsd:simpleType>
+        <xsd:restriction base="dms:Note"/>
+      </xsd:simpleType>
+    </xsd:element>
+    <xsd:element name="MediaServiceOCR" ma:index="14" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Note">
           <xsd:maxLength value="255"/>
         </xsd:restriction>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceDateTaken" ma:index="12" nillable="true" ma:displayName="MediaServiceDateTaken" ma:hidden="true" ma:internalName="MediaServiceDateTaken" ma:readOnly="true">
+    <xsd:element name="MediaServiceGenerationTime" ma:index="15" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaLengthInSeconds" ma:index="13" nillable="true" ma:displayName="MediaLengthInSeconds" ma:hidden="true" ma:internalName="MediaLengthInSeconds" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Unknown"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceGenerationTime" ma:index="16" nillable="true" ma:displayName="MediaServiceGenerationTime" ma:hidden="true" ma:internalName="MediaServiceGenerationTime" ma:readOnly="true">
+    <xsd:element name="MediaServiceEventHashCode" ma:index="16" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
       <xsd:simpleType>
         <xsd:restriction base="dms:Text"/>
       </xsd:simpleType>
     </xsd:element>
-    <xsd:element name="MediaServiceEventHashCode" ma:index="17" nillable="true" ma:displayName="MediaServiceEventHashCode" ma:hidden="true" ma:internalName="MediaServiceEventHashCode" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceOCR" ma:index="18" nillable="true" ma:displayName="Extracted Text" ma:internalName="MediaServiceOCR" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="lcf76f155ced4ddcb4097134ff3c332f" ma:index="20" nillable="true" ma:taxonomy="true" ma:internalName="lcf76f155ced4ddcb4097134ff3c332f" ma:taxonomyFieldName="MediaServiceImageTags" ma:displayName="Etiquetas de imagen" ma:readOnly="false" ma:fieldId="{5cf76f15-5ced-4ddc-b409-7134ff3c332f}" ma:taxonomyMulti="true" ma:sspId="71f7bd95-1200-4052-9a4e-dfdf006e181b" ma:termSetId="09814cd3-568e-fe90-9814-8d621ff8fb84" ma:anchorId="fba54fb3-c3e1-fe81-a776-ca4b69148c4d" ma:open="true" ma:isKeyword="false">
-      <xsd:complexType>
-        <xsd:sequence>
-          <xsd:element ref="pc:Terms" minOccurs="0" maxOccurs="1"/>
-        </xsd:sequence>
-      </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="MediaServiceObjectDetectorVersions" ma:index="21" nillable="true" ma:displayName="MediaServiceObjectDetectorVersions" ma:hidden="true" ma:indexed="true" ma:internalName="MediaServiceObjectDetectorVersions" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Text"/>
-      </xsd:simpleType>
-    </xsd:element>
-    <xsd:element name="MediaServiceSearchProperties" ma:index="22" nillable="true" ma:displayName="MediaServiceSearchProperties" ma:hidden="true" ma:internalName="MediaServiceSearchProperties" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note"/>
-      </xsd:simpleType>
-    </xsd:element>
   </xsd:schema>
-  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="1b6bb729-2ef5-410d-b4d4-7ced22c361d1" elementFormDefault="qualified">
+  <xsd:schema xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xs="http://www.w3.org/2001/XMLSchema" xmlns:dms="http://schemas.microsoft.com/office/2006/documentManagement/types" xmlns:pc="http://schemas.microsoft.com/office/infopath/2007/PartnerControls" targetNamespace="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99" elementFormDefault="qualified">
     <xsd:import namespace="http://schemas.microsoft.com/office/2006/documentManagement/types"/>
     <xsd:import namespace="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
-    <xsd:element name="SharedWithUsers" ma:index="14" nillable="true" ma:displayName="Compartido con" ma:internalName="SharedWithUsers" ma:readOnly="true">
+    <xsd:element name="TaxCatchAll" ma:index="12" nillable="true" ma:displayName="Taxonomy Catch All Column" ma:hidden="true" ma:list="{358d400d-8031-419e-a2bc-623ab747dbff}" ma:internalName="TaxCatchAll" ma:showField="CatchAllData" ma:web="dd2a1ab4-0a93-49a3-a811-47bf2ef55b99">
       <xsd:complexType>
         <xsd:complexContent>
-          <xsd:extension base="dms:UserMulti">
+          <xsd:extension base="dms:MultiChoiceLookup">
             <xsd:sequence>
-              <xsd:element name="UserInfo" minOccurs="0" maxOccurs="unbounded">
-                <xsd:complexType>
-                  <xsd:sequence>
-                    <xsd:element name="DisplayName" type="xsd:string" minOccurs="0"/>
-                    <xsd:element name="AccountId" type="dms:UserId" minOccurs="0" nillable="true"/>
-                    <xsd:element name="AccountType" type="xsd:string" minOccurs="0"/>
-                  </xsd:sequence>
-                </xsd:complexType>
-              </xsd:element>
+              <xsd:element name="Value" type="dms:Lookup" maxOccurs="unbounded" minOccurs="0" nillable="true"/>
             </xsd:sequence>
           </xsd:extension>
         </xsd:complexContent>
       </xsd:complexType>
-    </xsd:element>
-    <xsd:element name="SharedWithDetails" ma:index="15" nillable="true" ma:displayName="Detalles de uso compartido" ma:internalName="SharedWithDetails" ma:readOnly="true">
-      <xsd:simpleType>
-        <xsd:restriction base="dms:Note">
-          <xsd:maxLength value="255"/>
-        </xsd:restriction>
-      </xsd:simpleType>
     </xsd:element>
   </xsd:schema>
   <xsd:schema xmlns="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" xmlns:xsd="http://www.w3.org/2001/XMLSchema" xmlns:xsi="http://www.w3.org/2001/XMLSchema-instance" xmlns:dc="http://purl.org/dc/elements/1.1/" xmlns:dcterms="http://purl.org/dc/terms/" xmlns:odoc="http://schemas.microsoft.com/internal/obd" targetNamespace="http://schemas.openxmlformats.org/package/2006/metadata/core-properties" elementFormDefault="qualified" attributeFormDefault="unqualified" blockDefault="#all">
@@ -1704,8 +1678,8 @@
         <xsd:element ref="dc:creator" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dcterms:created" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:identifier" minOccurs="0" maxOccurs="1"/>
-        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Tipo de contenido"/>
-        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Título"/>
+        <xsd:element name="contentType" minOccurs="0" maxOccurs="1" type="xsd:string" ma:index="0" ma:displayName="Content Type"/>
+        <xsd:element ref="dc:title" minOccurs="0" maxOccurs="1" ma:index="4" ma:displayName="Title"/>
         <xsd:element ref="dc:subject" minOccurs="0" maxOccurs="1"/>
         <xsd:element ref="dc:description" minOccurs="0" maxOccurs="1"/>
         <xsd:element name="keywords" minOccurs="0" maxOccurs="1" type="xsd:string"/>
@@ -1794,19 +1768,24 @@
 </ct:contentTypeSchema>
 </file>
 
-<file path=customXml/item2.xml><?xml version="1.0" encoding="utf-8"?>
-<?mso-contentType ?>
-<FormTemplates xmlns="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms">
-  <Display>DocumentLibraryForm</Display>
-  <Edit>DocumentLibraryForm</Edit>
-  <New>DocumentLibraryForm</New>
-</FormTemplates>
-</file>
-
 <file path=customXml/itemProps1.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{C89D6BD8-8921-42B8-BA68-13955B2ADE5E}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{929CC985-20C0-4484-9E39-4911C6C9FE77}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/2006/metadata/properties"/>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/office/infopath/2007/PartnerControls"/>
+    <ds:schemaRef ds:uri="9c2c21c4-f980-47d5-be5b-1bb924ee96a2"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
 </file>
 
 <file path=customXml/itemProps2.xml><?xml version="1.0" encoding="utf-8"?>
-<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81950BC9-CD5C-4060-8364-5AFB53222010}"/>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{81950BC9-CD5C-4060-8364-5AFB53222010}">
+  <ds:schemaRefs>
+    <ds:schemaRef ds:uri="http://schemas.microsoft.com/sharepoint/v3/contenttype/forms"/>
+  </ds:schemaRefs>
+</ds:datastoreItem>
+</file>
+
+<file path=customXml/itemProps3.xml><?xml version="1.0" encoding="utf-8"?>
+<ds:datastoreItem xmlns:ds="http://schemas.openxmlformats.org/officeDocument/2006/customXml" ds:itemID="{F9A7403F-FAEA-4DAB-B45C-F987F5007D11}"/>
 </file>